--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-contact-relationship.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-contact-relationship.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="205">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Relationship</t>
+    <t>Relationship type</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -972,7 +972,9 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -984,7 +986,9 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -996,7 +1000,9 @@
       <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -1008,7 +1014,9 @@
       <c r="C5" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -1020,7 +1028,9 @@
       <c r="C6" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -1032,7 +1042,9 @@
       <c r="C7" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -1044,7 +1056,9 @@
       <c r="C8" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -1056,7 +1070,9 @@
       <c r="C9" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -1068,7 +1084,9 @@
       <c r="C10" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -1080,7 +1098,9 @@
       <c r="C11" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>62</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -1092,7 +1112,9 @@
       <c r="C12" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>64</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -1104,7 +1126,9 @@
       <c r="C13" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>66</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
@@ -1116,7 +1140,9 @@
       <c r="C14" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>68</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -1128,7 +1154,9 @@
       <c r="C15" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>70</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -1140,7 +1168,9 @@
       <c r="C16" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>72</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
@@ -1152,7 +1182,9 @@
       <c r="C17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="D17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>74</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
@@ -1164,7 +1196,9 @@
       <c r="C18" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="D18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>76</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
@@ -1176,7 +1210,9 @@
       <c r="C19" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="D19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
@@ -1188,7 +1224,9 @@
       <c r="C20" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="D20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>80</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
@@ -1200,7 +1238,9 @@
       <c r="C21" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>82</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
@@ -1212,7 +1252,9 @@
       <c r="C22" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="D22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>84</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
@@ -1224,7 +1266,9 @@
       <c r="C23" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="D23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>86</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
@@ -1236,7 +1280,9 @@
       <c r="C24" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="D24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>88</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
@@ -1248,7 +1294,9 @@
       <c r="C25" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="D25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>90</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
@@ -1260,7 +1308,9 @@
       <c r="C26" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="D26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>92</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
@@ -1272,7 +1322,9 @@
       <c r="C27" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="D27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>94</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
@@ -1284,7 +1336,9 @@
       <c r="C28" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="D28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>96</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
@@ -1296,7 +1350,9 @@
       <c r="C29" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="D29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>98</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
@@ -1308,7 +1364,9 @@
       <c r="C30" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="D30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>100</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
@@ -1320,7 +1378,9 @@
       <c r="C31" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="D31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>102</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
@@ -1332,7 +1392,9 @@
       <c r="C32" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="D32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>104</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
@@ -1344,7 +1406,9 @@
       <c r="C33" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="D33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>106</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
@@ -1356,7 +1420,9 @@
       <c r="C34" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="D34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>108</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
@@ -1368,7 +1434,9 @@
       <c r="C35" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="D35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>110</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
@@ -1380,7 +1448,9 @@
       <c r="C36" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="D36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>112</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
@@ -1392,7 +1462,9 @@
       <c r="C37" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="D37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>114</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
@@ -1404,7 +1476,9 @@
       <c r="C38" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="D38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>116</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
@@ -1416,7 +1490,9 @@
       <c r="C39" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="D39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>118</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
@@ -1428,7 +1504,9 @@
       <c r="C40" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="D40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>120</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
@@ -1440,7 +1518,9 @@
       <c r="C41" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="D41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>122</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
@@ -1452,7 +1532,9 @@
       <c r="C42" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="D42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>124</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
@@ -1464,7 +1546,9 @@
       <c r="C43" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="D43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>126</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
@@ -1476,7 +1560,9 @@
       <c r="C44" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="D44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>128</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
@@ -1488,7 +1574,9 @@
       <c r="C45" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="D45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>130</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
@@ -1500,7 +1588,9 @@
       <c r="C46" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="D46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>132</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
@@ -1512,7 +1602,9 @@
       <c r="C47" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="D47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>134</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
@@ -1524,7 +1616,9 @@
       <c r="C48" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="D48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>136</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
@@ -1536,7 +1630,9 @@
       <c r="C49" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="D49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>138</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
@@ -1548,7 +1644,9 @@
       <c r="C50" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="D50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>140</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
@@ -1560,7 +1658,9 @@
       <c r="C51" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="D51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>142</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
@@ -1572,7 +1672,9 @@
       <c r="C52" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="D52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>144</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
@@ -1584,7 +1686,9 @@
       <c r="C53" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="D53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>146</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
@@ -1596,7 +1700,9 @@
       <c r="C54" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="D54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>148</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
@@ -1608,7 +1714,9 @@
       <c r="C55" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="D55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>150</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
@@ -1620,7 +1728,9 @@
       <c r="C56" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="D56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>152</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
@@ -1632,7 +1742,9 @@
       <c r="C57" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="D57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>154</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
@@ -1644,7 +1756,9 @@
       <c r="C58" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="D58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>156</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
@@ -1656,7 +1770,9 @@
       <c r="C59" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="D59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>158</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
@@ -1668,7 +1784,9 @@
       <c r="C60" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="D60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>160</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
@@ -1680,7 +1798,9 @@
       <c r="C61" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="D61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>162</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
@@ -1692,7 +1812,9 @@
       <c r="C62" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="D62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>164</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
@@ -1704,7 +1826,9 @@
       <c r="C63" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="D63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>166</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
@@ -1716,7 +1840,9 @@
       <c r="C64" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="D64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>168</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
@@ -1728,7 +1854,9 @@
       <c r="C65" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="D65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>170</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
@@ -1740,7 +1868,9 @@
       <c r="C66" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="D66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>172</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
@@ -1752,7 +1882,9 @@
       <c r="C67" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="D67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>174</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
@@ -1764,7 +1896,9 @@
       <c r="C68" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="D68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>176</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
@@ -1776,7 +1910,9 @@
       <c r="C69" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="D69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>178</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
@@ -1788,7 +1924,9 @@
       <c r="C70" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="D70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>180</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
@@ -1800,7 +1938,9 @@
       <c r="C71" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="D71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>182</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
@@ -1812,7 +1952,9 @@
       <c r="C72" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="D72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>184</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
@@ -1824,7 +1966,9 @@
       <c r="C73" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="D73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>186</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
@@ -1836,7 +1980,9 @@
       <c r="C74" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="D74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>188</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
@@ -1848,7 +1994,9 @@
       <c r="C75" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="D75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>190</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
@@ -1860,7 +2008,9 @@
       <c r="C76" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="D76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>192</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
@@ -1872,7 +2022,9 @@
       <c r="C77" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="D77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>194</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
@@ -1884,7 +2036,9 @@
       <c r="C78" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="D78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>196</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
@@ -1896,7 +2050,9 @@
       <c r="C79" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="D79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>198</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
@@ -1908,7 +2064,9 @@
       <c r="C80" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="D80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>200</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
@@ -1920,7 +2078,9 @@
       <c r="C81" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="D81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>202</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
@@ -1932,7 +2092,9 @@
       <c r="C82" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="D82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>204</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-contact-relationship.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-contact-relationship.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="205">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Relationship type</t>
+    <t>Relationship</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -972,9 +972,7 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" t="s" s="2">
-        <v>44</v>
-      </c>
+      <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -986,9 +984,7 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" t="s" s="2">
-        <v>46</v>
-      </c>
+      <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -1000,9 +996,7 @@
       <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D4" t="s" s="2">
-        <v>48</v>
-      </c>
+      <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -1014,9 +1008,7 @@
       <c r="C5" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D5" t="s" s="2">
-        <v>50</v>
-      </c>
+      <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -1028,9 +1020,7 @@
       <c r="C6" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D6" t="s" s="2">
-        <v>52</v>
-      </c>
+      <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -1042,9 +1032,7 @@
       <c r="C7" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D7" t="s" s="2">
-        <v>54</v>
-      </c>
+      <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -1056,9 +1044,7 @@
       <c r="C8" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D8" t="s" s="2">
-        <v>56</v>
-      </c>
+      <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -1070,9 +1056,7 @@
       <c r="C9" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="D9" t="s" s="2">
-        <v>58</v>
-      </c>
+      <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -1084,9 +1068,7 @@
       <c r="C10" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D10" t="s" s="2">
-        <v>60</v>
-      </c>
+      <c r="D10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -1098,9 +1080,7 @@
       <c r="C11" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="D11" t="s" s="2">
-        <v>62</v>
-      </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -1112,9 +1092,7 @@
       <c r="C12" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="D12" t="s" s="2">
-        <v>64</v>
-      </c>
+      <c r="D12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -1126,9 +1104,7 @@
       <c r="C13" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="D13" t="s" s="2">
-        <v>66</v>
-      </c>
+      <c r="D13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
@@ -1140,9 +1116,7 @@
       <c r="C14" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="D14" t="s" s="2">
-        <v>68</v>
-      </c>
+      <c r="D14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -1154,9 +1128,7 @@
       <c r="C15" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="D15" t="s" s="2">
-        <v>70</v>
-      </c>
+      <c r="D15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -1168,9 +1140,7 @@
       <c r="C16" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="D16" t="s" s="2">
-        <v>72</v>
-      </c>
+      <c r="D16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
@@ -1182,9 +1152,7 @@
       <c r="C17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="D17" t="s" s="2">
-        <v>74</v>
-      </c>
+      <c r="D17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
@@ -1196,9 +1164,7 @@
       <c r="C18" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="D18" t="s" s="2">
-        <v>76</v>
-      </c>
+      <c r="D18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
@@ -1210,9 +1176,7 @@
       <c r="C19" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="D19" t="s" s="2">
-        <v>78</v>
-      </c>
+      <c r="D19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
@@ -1224,9 +1188,7 @@
       <c r="C20" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="D20" t="s" s="2">
-        <v>80</v>
-      </c>
+      <c r="D20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
@@ -1238,9 +1200,7 @@
       <c r="C21" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="D21" t="s" s="2">
-        <v>82</v>
-      </c>
+      <c r="D21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
@@ -1252,9 +1212,7 @@
       <c r="C22" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="D22" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="D22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
@@ -1266,9 +1224,7 @@
       <c r="C23" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="D23" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="D23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
@@ -1280,9 +1236,7 @@
       <c r="C24" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="D24" t="s" s="2">
-        <v>88</v>
-      </c>
+      <c r="D24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
@@ -1294,9 +1248,7 @@
       <c r="C25" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="D25" t="s" s="2">
-        <v>90</v>
-      </c>
+      <c r="D25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
@@ -1308,9 +1260,7 @@
       <c r="C26" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="D26" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="D26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
@@ -1322,9 +1272,7 @@
       <c r="C27" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="D27" t="s" s="2">
-        <v>94</v>
-      </c>
+      <c r="D27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
@@ -1336,9 +1284,7 @@
       <c r="C28" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="D28" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="D28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
@@ -1350,9 +1296,7 @@
       <c r="C29" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="D29" t="s" s="2">
-        <v>98</v>
-      </c>
+      <c r="D29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
@@ -1364,9 +1308,7 @@
       <c r="C30" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="D30" t="s" s="2">
-        <v>100</v>
-      </c>
+      <c r="D30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
@@ -1378,9 +1320,7 @@
       <c r="C31" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="D31" t="s" s="2">
-        <v>102</v>
-      </c>
+      <c r="D31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
@@ -1392,9 +1332,7 @@
       <c r="C32" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="D32" t="s" s="2">
-        <v>104</v>
-      </c>
+      <c r="D32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
@@ -1406,9 +1344,7 @@
       <c r="C33" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="D33" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="D33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
@@ -1420,9 +1356,7 @@
       <c r="C34" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="D34" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="D34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
@@ -1434,9 +1368,7 @@
       <c r="C35" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="D35" t="s" s="2">
-        <v>110</v>
-      </c>
+      <c r="D35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
@@ -1448,9 +1380,7 @@
       <c r="C36" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="D36" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="D36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
@@ -1462,9 +1392,7 @@
       <c r="C37" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="D37" t="s" s="2">
-        <v>114</v>
-      </c>
+      <c r="D37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
@@ -1476,9 +1404,7 @@
       <c r="C38" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="D38" t="s" s="2">
-        <v>116</v>
-      </c>
+      <c r="D38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
@@ -1490,9 +1416,7 @@
       <c r="C39" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="D39" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="D39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
@@ -1504,9 +1428,7 @@
       <c r="C40" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="D40" t="s" s="2">
-        <v>120</v>
-      </c>
+      <c r="D40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
@@ -1518,9 +1440,7 @@
       <c r="C41" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="D41" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="D41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
@@ -1532,9 +1452,7 @@
       <c r="C42" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="D42" t="s" s="2">
-        <v>124</v>
-      </c>
+      <c r="D42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
@@ -1546,9 +1464,7 @@
       <c r="C43" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="D43" t="s" s="2">
-        <v>126</v>
-      </c>
+      <c r="D43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
@@ -1560,9 +1476,7 @@
       <c r="C44" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="D44" t="s" s="2">
-        <v>128</v>
-      </c>
+      <c r="D44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
@@ -1574,9 +1488,7 @@
       <c r="C45" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="D45" t="s" s="2">
-        <v>130</v>
-      </c>
+      <c r="D45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
@@ -1588,9 +1500,7 @@
       <c r="C46" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="D46" t="s" s="2">
-        <v>132</v>
-      </c>
+      <c r="D46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
@@ -1602,9 +1512,7 @@
       <c r="C47" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="D47" t="s" s="2">
-        <v>134</v>
-      </c>
+      <c r="D47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
@@ -1616,9 +1524,7 @@
       <c r="C48" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="D48" t="s" s="2">
-        <v>136</v>
-      </c>
+      <c r="D48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
@@ -1630,9 +1536,7 @@
       <c r="C49" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="D49" t="s" s="2">
-        <v>138</v>
-      </c>
+      <c r="D49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
@@ -1644,9 +1548,7 @@
       <c r="C50" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="D50" t="s" s="2">
-        <v>140</v>
-      </c>
+      <c r="D50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
@@ -1658,9 +1560,7 @@
       <c r="C51" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="D51" t="s" s="2">
-        <v>142</v>
-      </c>
+      <c r="D51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
@@ -1672,9 +1572,7 @@
       <c r="C52" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="D52" t="s" s="2">
-        <v>144</v>
-      </c>
+      <c r="D52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
@@ -1686,9 +1584,7 @@
       <c r="C53" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="D53" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="D53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
@@ -1700,9 +1596,7 @@
       <c r="C54" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="D54" t="s" s="2">
-        <v>148</v>
-      </c>
+      <c r="D54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
@@ -1714,9 +1608,7 @@
       <c r="C55" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="D55" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="D55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
@@ -1728,9 +1620,7 @@
       <c r="C56" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="D56" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="D56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
@@ -1742,9 +1632,7 @@
       <c r="C57" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="D57" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="D57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
@@ -1756,9 +1644,7 @@
       <c r="C58" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="D58" t="s" s="2">
-        <v>156</v>
-      </c>
+      <c r="D58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
@@ -1770,9 +1656,7 @@
       <c r="C59" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="D59" t="s" s="2">
-        <v>158</v>
-      </c>
+      <c r="D59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
@@ -1784,9 +1668,7 @@
       <c r="C60" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="D60" t="s" s="2">
-        <v>160</v>
-      </c>
+      <c r="D60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
@@ -1798,9 +1680,7 @@
       <c r="C61" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="D61" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="D61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
@@ -1812,9 +1692,7 @@
       <c r="C62" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="D62" t="s" s="2">
-        <v>164</v>
-      </c>
+      <c r="D62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
@@ -1826,9 +1704,7 @@
       <c r="C63" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="D63" t="s" s="2">
-        <v>166</v>
-      </c>
+      <c r="D63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
@@ -1840,9 +1716,7 @@
       <c r="C64" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="D64" t="s" s="2">
-        <v>168</v>
-      </c>
+      <c r="D64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
@@ -1854,9 +1728,7 @@
       <c r="C65" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="D65" t="s" s="2">
-        <v>170</v>
-      </c>
+      <c r="D65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
@@ -1868,9 +1740,7 @@
       <c r="C66" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="D66" t="s" s="2">
-        <v>172</v>
-      </c>
+      <c r="D66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
@@ -1882,9 +1752,7 @@
       <c r="C67" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="D67" t="s" s="2">
-        <v>174</v>
-      </c>
+      <c r="D67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
@@ -1896,9 +1764,7 @@
       <c r="C68" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="D68" t="s" s="2">
-        <v>176</v>
-      </c>
+      <c r="D68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
@@ -1910,9 +1776,7 @@
       <c r="C69" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="D69" t="s" s="2">
-        <v>178</v>
-      </c>
+      <c r="D69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
@@ -1924,9 +1788,7 @@
       <c r="C70" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="D70" t="s" s="2">
-        <v>180</v>
-      </c>
+      <c r="D70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
@@ -1938,9 +1800,7 @@
       <c r="C71" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="D71" t="s" s="2">
-        <v>182</v>
-      </c>
+      <c r="D71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
@@ -1952,9 +1812,7 @@
       <c r="C72" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="D72" t="s" s="2">
-        <v>184</v>
-      </c>
+      <c r="D72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
@@ -1966,9 +1824,7 @@
       <c r="C73" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="D73" t="s" s="2">
-        <v>186</v>
-      </c>
+      <c r="D73" s="2"/>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
@@ -1980,9 +1836,7 @@
       <c r="C74" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="D74" t="s" s="2">
-        <v>188</v>
-      </c>
+      <c r="D74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
@@ -1994,9 +1848,7 @@
       <c r="C75" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="D75" t="s" s="2">
-        <v>190</v>
-      </c>
+      <c r="D75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
@@ -2008,9 +1860,7 @@
       <c r="C76" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="D76" t="s" s="2">
-        <v>192</v>
-      </c>
+      <c r="D76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
@@ -2022,9 +1872,7 @@
       <c r="C77" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="D77" t="s" s="2">
-        <v>194</v>
-      </c>
+      <c r="D77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
@@ -2036,9 +1884,7 @@
       <c r="C78" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="D78" t="s" s="2">
-        <v>196</v>
-      </c>
+      <c r="D78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
@@ -2050,9 +1896,7 @@
       <c r="C79" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="D79" t="s" s="2">
-        <v>198</v>
-      </c>
+      <c r="D79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
@@ -2064,9 +1908,7 @@
       <c r="C80" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="D80" t="s" s="2">
-        <v>200</v>
-      </c>
+      <c r="D80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
@@ -2078,9 +1920,7 @@
       <c r="C81" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="D81" t="s" s="2">
-        <v>202</v>
-      </c>
+      <c r="D81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
@@ -2092,9 +1932,7 @@
       <c r="C82" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="D82" t="s" s="2">
-        <v>204</v>
-      </c>
+      <c r="D82" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/www/ig/fhir/core/CodeSystem-fr-core-cs-contact-relationship.xlsx
+++ b/www/ig/fhir/core/CodeSystem-fr-core-cs-contact-relationship.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="205">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Relationship</t>
+    <t>Relationship type</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -972,7 +972,9 @@
       <c r="C2" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -984,7 +986,9 @@
       <c r="C3" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -996,7 +1000,9 @@
       <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
@@ -1008,7 +1014,9 @@
       <c r="C5" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -1020,7 +1028,9 @@
       <c r="C6" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
@@ -1032,7 +1042,9 @@
       <c r="C7" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -1044,7 +1056,9 @@
       <c r="C8" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
@@ -1056,7 +1070,9 @@
       <c r="C9" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
@@ -1068,7 +1084,9 @@
       <c r="C10" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
@@ -1080,7 +1098,9 @@
       <c r="C11" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>62</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -1092,7 +1112,9 @@
       <c r="C12" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>64</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
@@ -1104,7 +1126,9 @@
       <c r="C13" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>66</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
@@ -1116,7 +1140,9 @@
       <c r="C14" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>68</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -1128,7 +1154,9 @@
       <c r="C15" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>70</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
@@ -1140,7 +1168,9 @@
       <c r="C16" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>72</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
@@ -1152,7 +1182,9 @@
       <c r="C17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="D17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>74</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
@@ -1164,7 +1196,9 @@
       <c r="C18" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="D18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>76</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
@@ -1176,7 +1210,9 @@
       <c r="C19" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="D19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>78</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
@@ -1188,7 +1224,9 @@
       <c r="C20" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="D20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>80</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
@@ -1200,7 +1238,9 @@
       <c r="C21" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>82</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
@@ -1212,7 +1252,9 @@
       <c r="C22" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="D22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>84</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
@@ -1224,7 +1266,9 @@
       <c r="C23" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="D23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>86</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
@@ -1236,7 +1280,9 @@
       <c r="C24" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="D24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>88</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
@@ -1248,7 +1294,9 @@
       <c r="C25" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="D25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>90</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
@@ -1260,7 +1308,9 @@
       <c r="C26" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="D26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>92</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
@@ -1272,7 +1322,9 @@
       <c r="C27" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="D27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>94</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
@@ -1284,7 +1336,9 @@
       <c r="C28" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="D28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>96</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
@@ -1296,7 +1350,9 @@
       <c r="C29" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="D29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>98</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
@@ -1308,7 +1364,9 @@
       <c r="C30" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="D30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>100</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
@@ -1320,7 +1378,9 @@
       <c r="C31" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="D31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>102</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
@@ -1332,7 +1392,9 @@
       <c r="C32" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="D32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>104</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
@@ -1344,7 +1406,9 @@
       <c r="C33" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="D33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>106</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
@@ -1356,7 +1420,9 @@
       <c r="C34" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="D34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>108</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
@@ -1368,7 +1434,9 @@
       <c r="C35" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="D35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>110</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
@@ -1380,7 +1448,9 @@
       <c r="C36" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="D36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>112</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
@@ -1392,7 +1462,9 @@
       <c r="C37" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="D37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>114</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
@@ -1404,7 +1476,9 @@
       <c r="C38" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="D38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>116</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
@@ -1416,7 +1490,9 @@
       <c r="C39" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="D39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>118</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
@@ -1428,7 +1504,9 @@
       <c r="C40" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="D40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>120</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
@@ -1440,7 +1518,9 @@
       <c r="C41" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="D41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>122</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
@@ -1452,7 +1532,9 @@
       <c r="C42" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="D42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>124</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
@@ -1464,7 +1546,9 @@
       <c r="C43" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="D43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>126</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
@@ -1476,7 +1560,9 @@
       <c r="C44" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="D44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>128</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
@@ -1488,7 +1574,9 @@
       <c r="C45" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="D45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>130</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
@@ -1500,7 +1588,9 @@
       <c r="C46" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="D46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>132</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
@@ -1512,7 +1602,9 @@
       <c r="C47" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="D47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>134</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
@@ -1524,7 +1616,9 @@
       <c r="C48" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="D48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>136</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
@@ -1536,7 +1630,9 @@
       <c r="C49" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="D49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>138</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
@@ -1548,7 +1644,9 @@
       <c r="C50" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="D50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>140</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
@@ -1560,7 +1658,9 @@
       <c r="C51" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="D51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>142</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
@@ -1572,7 +1672,9 @@
       <c r="C52" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="D52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>144</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
@@ -1584,7 +1686,9 @@
       <c r="C53" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="D53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>146</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
@@ -1596,7 +1700,9 @@
       <c r="C54" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="D54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>148</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
@@ -1608,7 +1714,9 @@
       <c r="C55" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="D55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>150</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
@@ -1620,7 +1728,9 @@
       <c r="C56" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="D56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>152</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
@@ -1632,7 +1742,9 @@
       <c r="C57" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="D57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>154</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
@@ -1644,7 +1756,9 @@
       <c r="C58" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="D58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>156</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
@@ -1656,7 +1770,9 @@
       <c r="C59" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="D59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>158</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
@@ -1668,7 +1784,9 @@
       <c r="C60" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="D60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>160</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
@@ -1680,7 +1798,9 @@
       <c r="C61" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="D61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>162</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
@@ -1692,7 +1812,9 @@
       <c r="C62" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="D62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>164</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
@@ -1704,7 +1826,9 @@
       <c r="C63" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="D63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>166</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
@@ -1716,7 +1840,9 @@
       <c r="C64" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="D64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>168</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
@@ -1728,7 +1854,9 @@
       <c r="C65" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="D65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>170</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
@@ -1740,7 +1868,9 @@
       <c r="C66" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="D66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>172</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
@@ -1752,7 +1882,9 @@
       <c r="C67" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="D67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>174</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
@@ -1764,7 +1896,9 @@
       <c r="C68" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="D68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>176</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
@@ -1776,7 +1910,9 @@
       <c r="C69" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="D69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>178</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
@@ -1788,7 +1924,9 @@
       <c r="C70" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="D70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>180</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
@@ -1800,7 +1938,9 @@
       <c r="C71" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="D71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>182</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
@@ -1812,7 +1952,9 @@
       <c r="C72" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="D72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>184</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
@@ -1824,7 +1966,9 @@
       <c r="C73" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="D73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>186</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
@@ -1836,7 +1980,9 @@
       <c r="C74" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="D74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>188</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
@@ -1848,7 +1994,9 @@
       <c r="C75" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="D75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>190</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
@@ -1860,7 +2008,9 @@
       <c r="C76" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="D76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>192</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
@@ -1872,7 +2022,9 @@
       <c r="C77" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="D77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>194</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
@@ -1884,7 +2036,9 @@
       <c r="C78" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="D78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>196</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
@@ -1896,7 +2050,9 @@
       <c r="C79" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="D79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>198</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
@@ -1908,7 +2064,9 @@
       <c r="C80" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="D80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>200</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
@@ -1920,7 +2078,9 @@
       <c r="C81" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="D81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>202</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
@@ -1932,7 +2092,9 @@
       <c r="C82" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="D82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>204</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
